--- a/web/files/九龙-马头角-文曜.xlsx
+++ b/web/files/九龙-马头角-文曜.xlsx
@@ -5584,42 +5584,34 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I80" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>19043700</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>21043</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K80" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L80" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="K80" s="5" t="n">
+        <v>19043700</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>21043</v>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
@@ -6582,7 +6574,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -6592,7 +6584,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -7397,12 +7389,12 @@
 (26年-04月-20日)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
-        <is>
-          <t>C | 904呎 (3房)
--
--
-(待售)</t>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 905呎 (3房)
+$1904万
+$21,043/呎
+(26年-09月-09日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">

--- a/web/files/九龙-马头角-文曜.xlsx
+++ b/web/files/九龙-马头角-文曜.xlsx
@@ -2820,38 +2820,30 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>20785400</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>22993</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="K36" s="5" t="n">
+        <v>20785400</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>22993</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
@@ -6574,7 +6566,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>86</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -6584,7 +6576,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -6960,12 +6952,12 @@
 (25年-08月-18日)</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
--
--
-(待售)</t>
+$2079万
+$22,993/呎
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">

--- a/web/files/九龙-马头角-文曜.xlsx
+++ b/web/files/九龙-马头角-文曜.xlsx
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2194</v>
+        <v>2183</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>80000000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>36463</v>
+        <v>36647</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>80000000</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>36463</v>
+        <v>36647</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>12521200</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>19293</v>
+        <v>19263</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>12521200</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>19293</v>
+        <v>19263</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>19176200</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>21189</v>
+        <v>21213</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>19176200</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>21189</v>
+        <v>21213</v>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>19023700</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>21021</v>
+        <v>21044</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>19023700</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>21021</v>
+        <v>21044</v>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>12421500</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>19139</v>
+        <v>19110</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>12421500</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>19139</v>
+        <v>19110</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>12990600</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>20016</v>
+        <v>19986</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>12990600</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>20016</v>
+        <v>19986</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>12938600</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>19936</v>
+        <v>19906</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>12938600</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>19936</v>
+        <v>19906</v>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>18574500</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>20524</v>
+        <v>20547</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>18574500</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>20524</v>
+        <v>20547</v>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>12887400</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>19857</v>
+        <v>19827</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>12887400</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>19857</v>
+        <v>19827</v>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>12836200</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>19778</v>
+        <v>19748</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>12836200</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>19778</v>
+        <v>19748</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>12836200</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>19778</v>
+        <v>19748</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>12836200</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>19778</v>
+        <v>19748</v>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>19043700</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>21043</v>
+        <v>21066</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>19043700</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>21043</v>
+        <v>21066</v>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>12733800</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>19621</v>
+        <v>19590</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>12733800</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>19621</v>
+        <v>19590</v>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>17300600</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>19117</v>
+        <v>19138</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>17300600</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>19117</v>
+        <v>19138</v>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>11727700</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>18070</v>
+        <v>18043</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>11727700</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>18070</v>
+        <v>18043</v>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>16192300</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>17892</v>
+        <v>17912</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>16192300</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>17892</v>
+        <v>17912</v>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>11072200</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>17060</v>
+        <v>17034</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>11072200</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>17060</v>
+        <v>17034</v>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>16374600</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>19129</v>
+        <v>19152</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>16374600</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>19129</v>
+        <v>19152</v>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>10548700</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>16254</v>
+        <v>16229</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>10548700</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>16254</v>
+        <v>16229</v>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
@@ -6615,9 +6615,9 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 2194呎 (4+房)
+          <t>A | 2183呎 (4+房)
 $8000万
-$36,463/呎
+$36,647/呎
 (26年-07月-29日)</t>
         </is>
       </c>
@@ -7063,9 +7063,9 @@
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>B | 649呎 (2房)
+          <t>B | 650呎 (2房)
 $1252万
-$19,293/呎
+$19,263/呎
 (24年-12月-03日)</t>
         </is>
       </c>
@@ -7110,9 +7110,9 @@
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>C | 905呎 (3房)
+          <t>C | 904呎 (3房)
 $1918万
-$21,189/呎
+$21,213/呎
 (25年-06月-05日)</t>
         </is>
       </c>
@@ -7141,17 +7141,17 @@
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>B | 649呎 (2房)
+          <t>B | 650呎 (2房)
 $1242万
-$19,139/呎
+$19,110/呎
 (26年-03月-03日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>C | 905呎 (3房)
+          <t>C | 904呎 (3房)
 $1902万
-$21,021/呎
+$21,044/呎
 (26年-02月-27日)</t>
         </is>
       </c>
@@ -7180,15 +7180,15 @@
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>B | 649呎 (2房)
+          <t>B | 650呎 (2房)
 $1299万
-$20,016/呎
+$19,986/呎
 (26年-06月-01日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
         <is>
-          <t>C | 905呎 (3房)
+          <t>C | 904呎 (3房)
 -
 -
 (待售)</t>
@@ -7219,15 +7219,15 @@
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>B | 649呎 (2房)
+          <t>B | 650呎 (2房)
 $1294万
-$19,936/呎
+$19,906/呎
 (26年-06月-02日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
         <is>
-          <t>C | 905呎 (3房)
+          <t>C | 904呎 (3房)
 -
 -
 (待售)</t>
@@ -7258,17 +7258,17 @@
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>B | 649呎 (2房)
+          <t>B | 650呎 (2房)
 $1289万
-$19,857/呎
+$19,827/呎
 (26年-06月-03日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>C | 905呎 (3房)
+          <t>C | 904呎 (3房)
 $1857万
-$20,524/呎
+$20,547/呎
 (25年-01月-28日)</t>
         </is>
       </c>
@@ -7297,9 +7297,9 @@
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>B | 649呎 (2房)
+          <t>B | 650呎 (2房)
 $1284万
-$19,778/呎
+$19,748/呎
 (26年-06月-05日)</t>
         </is>
       </c>
@@ -7336,9 +7336,9 @@
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>B | 649呎 (2房)
+          <t>B | 650呎 (2房)
 $1284万
-$19,778/呎
+$19,748/呎
 (26年-06月-12日)</t>
         </is>
       </c>
@@ -7375,17 +7375,17 @@
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>B | 649呎 (2房)
+          <t>B | 650呎 (2房)
 $1273万
-$19,621/呎
+$19,590/呎
 (26年-04月-20日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>C | 905呎 (3房)
+          <t>C | 904呎 (3房)
 $1904万
-$21,043/呎
+$21,066/呎
 (26年-09月-09日)</t>
         </is>
       </c>
@@ -7414,17 +7414,17 @@
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>B | 649呎 (2房)
+          <t>B | 650呎 (2房)
 $1173万
-$18,070/呎
+$18,043/呎
 (25年-10月-24日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>C | 905呎 (2房)
+          <t>C | 904呎 (2房)
 $1730万
-$19,117/呎
+$19,138/呎
 (25年-04月-25日)</t>
         </is>
       </c>
@@ -7453,17 +7453,17 @@
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>B | 649呎 (2房)
+          <t>B | 650呎 (2房)
 $1107万
-$17,060/呎
+$17,034/呎
 (24年-10月-02日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
         <is>
-          <t>C | 905呎 (2房)
+          <t>C | 904呎 (2房)
 $1619万
-$17,892/呎
+$17,912/呎
 (25年-11月-03日)</t>
         </is>
       </c>
@@ -7492,17 +7492,17 @@
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>B | 649呎 (2房)
+          <t>B | 650呎 (2房)
 $1055万
-$16,254/呎
+$16,229/呎
 (23年-10月-26日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>C | 856呎 (2房)
+          <t>C | 855呎 (2房)
 $1637万
-$19,129/呎
+$19,152/呎
 (23年-10月-31日)</t>
         </is>
       </c>
